--- a/demo_data/medications.xlsx
+++ b/demo_data/medications.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UHID-1005</t>
+          <t>UHID-1001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,21 +501,21 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Dr. Arjun Verma</t>
+          <t>Dr. Kavita Nair</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
@@ -526,7 +526,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UHID-1004</t>
+          <t>UHID-1008</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -551,21 +551,21 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Dr. Manish Gupta</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4">
@@ -576,7 +576,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UHID-1014</t>
+          <t>UHID-1012</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -601,21 +601,21 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Dr. Deepa Iyer</t>
+          <t>Dr. Priya Mehta</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UHID-1004</t>
+          <t>UHID-1003</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>Oral</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>95</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6">
@@ -676,7 +676,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UHID-1018</t>
+          <t>UHID-1016</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -696,26 +696,26 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Subcutaneous</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Dr. Manish Gupta</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -726,7 +726,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UHID-1004</t>
+          <t>UHID-1003</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -746,26 +746,26 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oral</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Dr. Rajesh Kumar</t>
+          <t>Dr. Priya Mehta</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
@@ -776,7 +776,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UHID-1012</t>
+          <t>UHID-1009</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -801,21 +801,21 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Dr. Anita Singh</t>
+          <t>Dr. Vikram Rao</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
@@ -826,7 +826,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UHID-1004</t>
+          <t>UHID-1009</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -846,26 +846,26 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Subcutaneous</t>
+          <t>Oral</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Dr. Anita Singh</t>
+          <t>Dr. Priya Mehta</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -876,7 +876,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UHID-1009</t>
+          <t>UHID-1011</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -901,21 +901,21 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Dr. Suresh Reddy</t>
+          <t>Dr. Deepa Iyer</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11">
@@ -926,7 +926,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UHID-1019</t>
+          <t>UHID-1017</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -951,21 +951,21 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Dr. Deepa Iyer</t>
+          <t>Dr. Suresh Reddy</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12">
@@ -976,7 +976,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UHID-1013</t>
+          <t>UHID-1007</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1001,21 +1001,21 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Dr. Deepa Iyer</t>
+          <t>Dr. Arjun Verma</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -1051,21 +1051,21 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Dr. Suresh Reddy</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UHID-1000</t>
+          <t>UHID-1005</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1101,21 +1101,21 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Dr. Anita Singh</t>
+          <t>Dr. Priya Mehta</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UHID-1008</t>
+          <t>UHID-1004</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oral</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UHID-1001</t>
+          <t>UHID-1002</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1196,26 +1196,26 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oral</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Dr. Kavita Nair</t>
+          <t>Dr. Arjun Verma</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>71</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UHID-1005</t>
+          <t>UHID-1006</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1251,21 +1251,21 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Dr. Deepa Iyer</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>61</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UHID-1014</t>
+          <t>UHID-1003</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1296,26 +1296,26 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Subcutaneous</t>
+          <t>Oral</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Dr. Anita Singh</t>
+          <t>Dr. Deepa Iyer</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UHID-1018</t>
+          <t>UHID-1011</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1346,26 +1346,26 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Subcutaneous</t>
+          <t>Oral</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Dr. Arjun Verma</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UHID-1003</t>
+          <t>UHID-1015</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1396,26 +1396,26 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Oral</t>
+          <t>Subcutaneous</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Dr. Kavita Nair</t>
+          <t>Dr. Deepa Iyer</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UHID-1012</t>
+          <t>UHID-1019</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1451,21 +1451,21 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Dr. Manish Gupta</t>
+          <t>Dr. Priya Mehta</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UHID-1008</t>
+          <t>UHID-1010</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1501,21 +1501,21 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Dr. Kavita Nair</t>
+          <t>Dr. Arjun Verma</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>92</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UHID-1016</t>
+          <t>UHID-1010</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1546,26 +1546,26 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oral</t>
+          <t>Subcutaneous</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Dr. Arjun Verma</t>
+          <t>Dr. Deepa Iyer</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UHID-1007</t>
+          <t>UHID-1000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1596,26 +1596,26 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Oral</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Dr. Rajesh Kumar</t>
+          <t>Dr. Deepa Iyer</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>UHID-1006</t>
+          <t>UHID-1008</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1646,26 +1646,26 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oral</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Dr. Kavita Nair</t>
+          <t>Dr. Deepa Iyer</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UHID-1000</t>
+          <t>UHID-1002</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1696,26 +1696,26 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Oral</t>
+          <t>Subcutaneous</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Dr. Arjun Verma</t>
+          <t>Dr. Kavita Nair</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
